--- a/대시보드노출제외상품.xlsx
+++ b/대시보드노출제외상품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNIX117\♥Claude\02_Issue별\06_Stock-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FC0585-0F58-4541-9105-607640065792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87B11E3-E08D-4968-A108-2E4A38052E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7B9D2AA-30FD-4CA4-BC5E-D41084FA95F9}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
   <si>
     <t>제품명</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>UN-C1940</t>
+  </si>
+  <si>
+    <t>UN-A9500TEST</t>
+  </si>
+  <si>
+    <t>UCI-A9525TEST</t>
   </si>
 </sst>
 </file>
@@ -12214,24 +12220,68 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,3,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="D16" s="2">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,4,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,5,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="F16" s="2">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <f>VLOOKUP($A16,[1]상품코드집!$B:$H,7,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="A17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="2">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,3,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="D17" s="2">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,4,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,5,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="F17" s="2">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="str">
+        <f>VLOOKUP($A17,[1]상품코드집!$B:$H,7,0)</f>
+        <v>기타</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1"/>

--- a/대시보드노출제외상품.xlsx
+++ b/대시보드노출제외상품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNIX117\♥Claude\02_Issue별\06_Stock-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87B11E3-E08D-4968-A108-2E4A38052E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3419364B-B44D-4BF0-9ABA-5DF9E366CCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7B9D2AA-30FD-4CA4-BC5E-D41084FA95F9}"/>
   </bookViews>
@@ -85,12 +85,15 @@
     <comment ref="A11" authorId="1" shapeId="0" xr:uid="{C2D79DB1-5FA5-4A73-88F4-54CF68BC590A}">
       <text/>
     </comment>
+    <comment ref="A18" authorId="1" shapeId="0" xr:uid="{85336856-5757-4412-B614-700645FDA511}">
+      <text/>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>제품명</t>
   </si>
@@ -219,6 +222,10 @@
   </si>
   <si>
     <t>UCI-A9525TEST</t>
+  </si>
+  <si>
+    <t>UCI-A4140</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -12284,14 +12291,36 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,3,0)</f>
+        <v>고데기</v>
+      </c>
+      <c r="D18" s="2">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,4,0)</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,5,0)</f>
+        <v>봉형</v>
+      </c>
+      <c r="F18" s="2">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="str">
+        <f>VLOOKUP($A18,[1]상품코드집!$B:$H,7,0)</f>
+        <v>봉형</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1"/>
